--- a/super-admin-paneli/Ornek_Exceller/Dersler_Ornek.xlsx
+++ b/super-admin-paneli/Ornek_Exceller/Dersler_Ornek.xlsx
@@ -397,28 +397,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Kod</v>
+        <v>kod</v>
       </c>
       <c r="B1" t="str">
-        <v>Ad</v>
+        <v>ad</v>
       </c>
       <c r="C1" t="str">
-        <v>Teori</v>
+        <v>teori</v>
       </c>
       <c r="D1" t="str">
-        <v>Lab</v>
+        <v>lab</v>
       </c>
       <c r="E1" t="str">
-        <v>Kredi</v>
+        <v>kredi</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>CS101</v>
+        <v>BLM101</v>
       </c>
       <c r="B2" t="str">
         <v>Bilgisayar Bilimlerine Giriş</v>
@@ -435,41 +435,126 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>MATH101</v>
+        <v>BLM102</v>
       </c>
       <c r="B3" t="str">
-        <v>Kalkülüs I</v>
+        <v>Programlama I</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>PHY101</v>
+        <v>MAT101</v>
       </c>
       <c r="B4" t="str">
-        <v>Fizik I</v>
+        <v>Kalkülüs I</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>FIZ101</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Fizik I</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>BLM201</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Veri Yapıları</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>BLM301</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Veritabanı Yönetim Sistemleri</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>BLM302</v>
+      </c>
+      <c r="B8" t="str">
+        <v>İşletim Sistemleri</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ENG101</v>
+      </c>
+      <c r="B9" t="str">
+        <v>İngilizce I</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
   </ignoredErrors>
 </worksheet>
 </file>